--- a/BVSimulationFiles/75.xlsx
+++ b/BVSimulationFiles/75.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.002173913043478261</v>
+        <v>0.004347826086956522</v>
       </c>
       <c r="C2" t="n">
-        <v>0.002122181051079939</v>
+        <v>0.004244362102159878</v>
       </c>
       <c r="D2" t="n">
-        <v>0.002061264803224258</v>
+        <v>0.004122529606448516</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001993320395105952</v>
+        <v>0.003986640790211904</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001920182286218682</v>
+        <v>0.003840364572437364</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001843404479934556</v>
+        <v>0.003686808959869112</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001764296825192162</v>
+        <v>0.003528593650384324</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001683956991448237</v>
+        <v>0.003367913982896474</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001603298607719339</v>
+        <v>0.003206597215438678</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001523076002665711</v>
+        <v>0.003046152005331422</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001443905934570873</v>
+        <v>0.002887811869141746</v>
       </c>
       <c r="M2" t="n">
-        <v>0.001366286657139327</v>
+        <v>0.002732573314278654</v>
       </c>
       <c r="N2" t="n">
-        <v>0.001290614628725676</v>
+        <v>0.002581229257451352</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001217199138433264</v>
+        <v>0.002434398276866528</v>
       </c>
       <c r="P2" t="n">
-        <v>0.001146275092041341</v>
+        <v>0.002292550184082682</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.001078014173545037</v>
+        <v>0.002156028347090074</v>
       </c>
       <c r="R2" t="n">
-        <v>0.001012534573870906</v>
+        <v>0.002025069147741812</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0009499094567483364</v>
+        <v>0.001899818913496673</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0008901743124922388</v>
+        <v>0.001780348624984478</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0008333333333333334</v>
+        <v>0.001666666666666667</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002173913043478261</v>
+        <v>0.004347826086956522</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002122181051079939</v>
+        <v>0.004244362102159878</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002061264803224258</v>
+        <v>0.004122529606448516</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001993320395105952</v>
+        <v>0.003986640790211904</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001920182286218682</v>
+        <v>0.003840364572437364</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001843404479934556</v>
+        <v>0.003686808959869112</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001764296825192162</v>
+        <v>0.003528593650384324</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001683956991448237</v>
+        <v>0.003367913982896474</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001603298607719339</v>
+        <v>0.003206597215438678</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001523076002665711</v>
+        <v>0.003046152005331422</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001443905934570873</v>
+        <v>0.002887811869141746</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001366286657139327</v>
+        <v>0.002732573314278654</v>
       </c>
       <c r="N3" t="n">
-        <v>0.001290614628725676</v>
+        <v>0.002581229257451352</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001217199138433264</v>
+        <v>0.002434398276866528</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001146275092041341</v>
+        <v>0.002292550184082682</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.001078014173545037</v>
+        <v>0.002156028347090074</v>
       </c>
       <c r="R3" t="n">
-        <v>0.001012534573870906</v>
+        <v>0.002025069147741812</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0009499094567483364</v>
+        <v>0.001899818913496673</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0008901743124922388</v>
+        <v>0.001780348624984478</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0008333333333333334</v>
+        <v>0.001666666666666667</v>
       </c>
     </row>
   </sheetData>

--- a/BVSimulationFiles/75.xlsx
+++ b/BVSimulationFiles/75.xlsx
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.004347826086956522</v>
+        <v>0.04347826086956522</v>
       </c>
       <c r="C2" t="n">
-        <v>0.004244362102159878</v>
+        <v>0.04244362102159878</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004122529606448516</v>
+        <v>0.04122529606448516</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003986640790211904</v>
+        <v>0.03986640790211904</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003840364572437364</v>
+        <v>0.03840364572437364</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003686808959869112</v>
+        <v>0.03686808959869112</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003528593650384324</v>
+        <v>0.03528593650384324</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003367913982896474</v>
+        <v>0.03367913982896474</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003206597215438678</v>
+        <v>0.03206597215438678</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003046152005331422</v>
+        <v>0.03046152005331422</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002887811869141746</v>
+        <v>0.02887811869141746</v>
       </c>
       <c r="M2" t="n">
-        <v>0.002732573314278654</v>
+        <v>0.02732573314278654</v>
       </c>
       <c r="N2" t="n">
-        <v>0.002581229257451352</v>
+        <v>0.02581229257451352</v>
       </c>
       <c r="O2" t="n">
-        <v>0.002434398276866528</v>
+        <v>0.02434398276866528</v>
       </c>
       <c r="P2" t="n">
-        <v>0.002292550184082682</v>
+        <v>0.02292550184082682</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.002156028347090074</v>
+        <v>0.02156028347090074</v>
       </c>
       <c r="R2" t="n">
-        <v>0.002025069147741812</v>
+        <v>0.02025069147741812</v>
       </c>
       <c r="S2" t="n">
-        <v>0.001899818913496673</v>
+        <v>0.01899818913496673</v>
       </c>
       <c r="T2" t="n">
-        <v>0.001780348624984478</v>
+        <v>0.01780348624984478</v>
       </c>
       <c r="U2" t="n">
-        <v>0.001666666666666667</v>
+        <v>0.01666666666666667</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.004347826086956522</v>
+        <v>0.04347826086956522</v>
       </c>
       <c r="C3" t="n">
-        <v>0.004244362102159878</v>
+        <v>0.04244362102159878</v>
       </c>
       <c r="D3" t="n">
-        <v>0.004122529606448516</v>
+        <v>0.04122529606448516</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003986640790211904</v>
+        <v>0.03986640790211904</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003840364572437364</v>
+        <v>0.03840364572437364</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003686808959869112</v>
+        <v>0.03686808959869112</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003528593650384324</v>
+        <v>0.03528593650384324</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003367913982896474</v>
+        <v>0.03367913982896474</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003206597215438678</v>
+        <v>0.03206597215438678</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003046152005331422</v>
+        <v>0.03046152005331422</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002887811869141746</v>
+        <v>0.02887811869141746</v>
       </c>
       <c r="M3" t="n">
-        <v>0.002732573314278654</v>
+        <v>0.02732573314278654</v>
       </c>
       <c r="N3" t="n">
-        <v>0.002581229257451352</v>
+        <v>0.02581229257451352</v>
       </c>
       <c r="O3" t="n">
-        <v>0.002434398276866528</v>
+        <v>0.02434398276866528</v>
       </c>
       <c r="P3" t="n">
-        <v>0.002292550184082682</v>
+        <v>0.02292550184082682</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.002156028347090074</v>
+        <v>0.02156028347090074</v>
       </c>
       <c r="R3" t="n">
-        <v>0.002025069147741812</v>
+        <v>0.02025069147741812</v>
       </c>
       <c r="S3" t="n">
-        <v>0.001899818913496673</v>
+        <v>0.01899818913496673</v>
       </c>
       <c r="T3" t="n">
-        <v>0.001780348624984478</v>
+        <v>0.01780348624984478</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001666666666666667</v>
+        <v>0.01666666666666667</v>
       </c>
     </row>
   </sheetData>

--- a/BVSimulationFiles/75.xlsx
+++ b/BVSimulationFiles/75.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -421,61 +421,34 @@
         <v>0</v>
       </c>
       <c r="C1" t="n">
-        <v>0.05621631578947369</v>
+        <v>0.03683103448275862</v>
       </c>
       <c r="D1" t="n">
-        <v>0.1124326315789474</v>
+        <v>0.07366206896551725</v>
       </c>
       <c r="E1" t="n">
-        <v>0.1686489473684211</v>
+        <v>0.1104931034482759</v>
       </c>
       <c r="F1" t="n">
-        <v>0.2248652631578948</v>
+        <v>0.1473241379310345</v>
       </c>
       <c r="G1" t="n">
-        <v>0.2810815789473685</v>
+        <v>0.1841551724137931</v>
       </c>
       <c r="H1" t="n">
-        <v>0.3372978947368421</v>
+        <v>0.2209862068965517</v>
       </c>
       <c r="I1" t="n">
-        <v>0.3935142105263158</v>
+        <v>0.2578172413793103</v>
       </c>
       <c r="J1" t="n">
-        <v>0.4497305263157895</v>
+        <v>0.294648275862069</v>
       </c>
       <c r="K1" t="n">
-        <v>0.5059468421052632</v>
+        <v>0.3314793103448276</v>
       </c>
       <c r="L1" t="n">
-        <v>0.5621631578947369</v>
-      </c>
-      <c r="M1" t="n">
-        <v>0.6183794736842105</v>
-      </c>
-      <c r="N1" t="n">
-        <v>0.6745957894736843</v>
-      </c>
-      <c r="O1" t="n">
-        <v>0.730812105263158</v>
-      </c>
-      <c r="P1" t="n">
-        <v>0.7870284210526316</v>
-      </c>
-      <c r="Q1" t="n">
-        <v>0.8432447368421053</v>
-      </c>
-      <c r="R1" t="n">
-        <v>0.899461052631579</v>
-      </c>
-      <c r="S1" t="n">
-        <v>0.9556773684210528</v>
-      </c>
-      <c r="T1" t="n">
-        <v>1.011893684210526</v>
-      </c>
-      <c r="U1" t="n">
-        <v>1.06811</v>
+        <v>0.3683103448275862</v>
       </c>
     </row>
     <row r="2">
@@ -483,64 +456,37 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04347826086956522</v>
+        <v>0.1323531954604039</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04244362102159878</v>
+        <v>0.1333466228977991</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04122529606448516</v>
+        <v>0.1321929664807882</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03986640790211904</v>
+        <v>0.1293935543521293</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03840364572437364</v>
+        <v>0.1253602738619816</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03686808959869112</v>
+        <v>0.1204298230433116</v>
       </c>
       <c r="H2" t="n">
-        <v>0.03528593650384324</v>
+        <v>0.1148758291027697</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03367913982896474</v>
+        <v>0.1089191406914898</v>
       </c>
       <c r="J2" t="n">
-        <v>0.03206597215438678</v>
+        <v>0.1027365578034398</v>
       </c>
       <c r="K2" t="n">
-        <v>0.03046152005331422</v>
+        <v>0.09646822611574551</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02887811869141746</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.02732573314278654</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.02581229257451352</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.02434398276866528</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.02292550184082682</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.02156028347090074</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.02025069147741812</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.01899818913496673</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.01780348624984478</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.01666666666666667</v>
+        <v>0.09022389064166404</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +494,37 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.04347826086956522</v>
+        <v>0.1323531954604039</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04244362102159878</v>
+        <v>0.1333466228977991</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04122529606448516</v>
+        <v>0.1321929664807882</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03986640790211904</v>
+        <v>0.1293935543521293</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03840364572437364</v>
+        <v>0.1253602738619816</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03686808959869112</v>
+        <v>0.1204298230433116</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03528593650384324</v>
+        <v>0.1148758291027697</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03367913982896474</v>
+        <v>0.1089191406914898</v>
       </c>
       <c r="J3" t="n">
-        <v>0.03206597215438678</v>
+        <v>0.1027365578034398</v>
       </c>
       <c r="K3" t="n">
-        <v>0.03046152005331422</v>
+        <v>0.09646822611574551</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02887811869141746</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.02732573314278654</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.02581229257451352</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.02434398276866528</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.02292550184082682</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.02156028347090074</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.02025069147741812</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.01899818913496673</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0.01780348624984478</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0.01666666666666667</v>
+        <v>0.09022389064166404</v>
       </c>
     </row>
   </sheetData>
